--- a/artfynd/A 34205-2021 artfynd.xlsx
+++ b/artfynd/A 34205-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34205-2021 artfynd.xlsx
+++ b/artfynd/A 34205-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2275,6 +2275,115 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126020943</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57933</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>496477</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6575000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34205-2021 artfynd.xlsx
+++ b/artfynd/A 34205-2021 artfynd.xlsx
@@ -2280,7 +2280,7 @@
         <v>126020943</v>
       </c>
       <c r="B15" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34205-2021 artfynd.xlsx
+++ b/artfynd/A 34205-2021 artfynd.xlsx
@@ -2280,7 +2280,7 @@
         <v>126020943</v>
       </c>
       <c r="B15" t="n">
-        <v>57934</v>
+        <v>57938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34205-2021 artfynd.xlsx
+++ b/artfynd/A 34205-2021 artfynd.xlsx
@@ -2280,7 +2280,7 @@
         <v>126020943</v>
       </c>
       <c r="B15" t="n">
-        <v>57938</v>
+        <v>57939</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34205-2021 artfynd.xlsx
+++ b/artfynd/A 34205-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94850608</v>
+        <v>94852857</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496779.7918347684</v>
+        <v>496484</v>
       </c>
       <c r="R2" t="n">
-        <v>6575299.04420217</v>
+        <v>6575032</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,22 +767,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Tverling, Owe Nilsson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94850753</v>
+        <v>96133457</v>
       </c>
       <c r="B3" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,40 +785,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>4394</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örebro, Nrk</t>
+          <t>Garphytteklint, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496785.3743721104</v>
+        <v>496705</v>
       </c>
       <c r="R3" t="n">
-        <v>6575249.013790471</v>
+        <v>6575132</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,70 +864,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Therese Steiner, Owe Nilsson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94850538</v>
+        <v>101863579</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>4740</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Örebro, Nrk</t>
+          <t>Garphytteklint, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496771.1469865729</v>
+        <v>496517</v>
       </c>
       <c r="R4" t="n">
-        <v>6575355.712493138</v>
+        <v>6575016</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,22 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,70 +965,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94850414</v>
+        <v>101863547</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>5754</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Örebro, Nrk</t>
+          <t>Garphytteklint, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496779.367610651</v>
+        <v>496457</v>
       </c>
       <c r="R5" t="n">
-        <v>6575401.646186851</v>
+        <v>6575014</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,22 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,33 +1066,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94867003</v>
+        <v>101661161</v>
       </c>
       <c r="B6" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,50 +1096,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>100087</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skräddartorpet, Nrk</t>
+          <t>Garphytteklint, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496791.5725068751</v>
+        <v>496497</v>
       </c>
       <c r="R6" t="n">
-        <v>6575322.004970565</v>
+        <v>6575030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,34 +1162,14 @@
           <t>Tysslinge</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>T-Öre-7295</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ingen blomning. Endast bladrosetter. På stigens västra kant i backen norr om torplämningen.</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,65 +1178,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Stigkant, gräsbevuxen, blandskog.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95151704</v>
+        <v>101661172</v>
       </c>
       <c r="B7" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102976</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1321,27 +1229,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skräddartorpet, Garphytteklint, Flyhagen Ånnabodavägen.Garphyttan, Nrk</t>
+          <t>Garphytteklint, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496780.8882116664</v>
+        <v>496781</v>
       </c>
       <c r="R7" t="n">
-        <v>6575385.820945065</v>
+        <v>6575277</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,22 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2021-07-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>06:30</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,27 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ronnie Lindqvist</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ronnie Lindqvist</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96133457</v>
+        <v>101661175</v>
       </c>
       <c r="B8" t="n">
-        <v>86161</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4394</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Honungsvaxskivling</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1447,24 +1342,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Garphytteklint, Nrk</t>
+          <t>Flyhagenvägen, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496704.9885152943</v>
+        <v>496784</v>
       </c>
       <c r="R8" t="n">
-        <v>6575132.183480927</v>
+        <v>6575375</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1488,22 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,86 +1400,78 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101661177</v>
+        <v>95151704</v>
       </c>
       <c r="B9" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flyhagenvägen, Nrk</t>
+          <t>Skräddartorpet, Garphytteklint, Flyhagen Ånnabodavägen.Garphyttan, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496783.9467672927</v>
+        <v>496781</v>
       </c>
       <c r="R9" t="n">
-        <v>6575374.588409643</v>
+        <v>6575385</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,22 +1495,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,76 +1525,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Ronnie Lindqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Ronnie Lindqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101661173</v>
+        <v>95269384</v>
       </c>
       <c r="B10" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Garphytteklint, Nrk</t>
+          <t>Garphytte klint, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496781.3068471607</v>
+        <v>496488</v>
       </c>
       <c r="R10" t="n">
-        <v>6575276.582489948</v>
+        <v>6575036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1741,22 +1610,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,76 +1630,71 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101661223</v>
+        <v>95292929</v>
       </c>
       <c r="B11" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205995</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Garphytteklint, Nrk</t>
+          <t>Garphytteklintområdet, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496783.9467672927</v>
+        <v>496760</v>
       </c>
       <c r="R11" t="n">
-        <v>6575374.588409643</v>
+        <v>6575372</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,22 +1721,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Inventering av skogsgruppen inom Naturskyddsföreningen i Örebro län</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,53 +1742,53 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101661175</v>
+        <v>126020943</v>
       </c>
       <c r="B12" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100092</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1947,29 +1796,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flyhagenvägen, Nrk</t>
+          <t>Garphytteklint, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496783.9467672927</v>
+        <v>496477</v>
       </c>
       <c r="R12" t="n">
-        <v>6575374.588409643</v>
+        <v>6575000</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1993,22 +1840,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,27 +1860,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101661172</v>
+        <v>95269369</v>
       </c>
       <c r="B13" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100092</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2073,26 +1905,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Garphytteklint, Nrk</t>
+          <t>Garphytte klint, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496781.3068471607</v>
+        <v>496512</v>
       </c>
       <c r="R13" t="n">
-        <v>6575276.582489948</v>
+        <v>6575031</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2119,22 +1945,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2149,27 +1965,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101863579</v>
+        <v>101661178</v>
       </c>
       <c r="B14" t="n">
-        <v>90282</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,40 +1988,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4740</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Garphytteklint, Nrk</t>
+          <t>Flyhagenvägen, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496517.204920985</v>
+        <v>496784</v>
       </c>
       <c r="R14" t="n">
-        <v>6575015.958877521</v>
+        <v>6575375</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2234,22 +2056,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2258,29 +2070,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126020943</v>
+        <v>101661159</v>
       </c>
       <c r="B15" t="n">
-        <v>57939</v>
+        <v>56816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2288,49 +2099,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Garphytteklint, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496477</v>
+        <v>496497</v>
       </c>
       <c r="R15" t="n">
-        <v>6575000</v>
+        <v>6575030</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2354,12 +2167,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2021-07-31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2374,15 +2187,2130 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>101661173</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>496781</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6575277</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-07-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>101661177</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Flyhagenvägen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>496784</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6575375</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-07-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>95655874</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skräddartorpet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>496799</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6575273</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>94850608</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>496780</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6575299</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>David Tverling, Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>94850683</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496792</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6575364</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner, Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>94850717</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496814</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6575276</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner, Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>94850753</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>496786</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6575249</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner, Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>95292958</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Garphytteklintområdet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>496789</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6575350</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Inventering av skogsgruppen inom Naturskyddsföreningen i Örebro län</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>traktorväg</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>94850562</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>496783</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6575347</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>David Tverling, Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>94867003</v>
+      </c>
+      <c r="B25" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skräddartorpet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>496792</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6575322</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Öre-0181</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ingen blomning. Endast bladrosetter. På stigens västra kant i backen norr om torplämningen.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Stigkant, gräsbevuxen, blandskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>94850404</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>496786</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6575382</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>94850414</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>496780</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6575402</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>94850538</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>496771</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6575355</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>95573284</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>496628</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6575076</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-08-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-08-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Skog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>95573285</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>496762</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6575288</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-08-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-08-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Skog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>93186954</v>
+      </c>
+      <c r="B31" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>496818</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6575480</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Blandskog, gran gåal, hägg och hassel</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>95573283</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>496628</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6575076</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-08-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-08-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Skog på kalkrik mark</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>95269373</v>
+      </c>
+      <c r="B33" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Garphytte klint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>496490</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6575034</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-07-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-07-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>101908730</v>
+      </c>
+      <c r="B34" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>496462</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6575023</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>101863530</v>
+      </c>
+      <c r="B35" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>496454</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6575005</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-08-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-08-22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
